--- a/TestFiles/ExcelFiles/AscScheme.xlsx
+++ b/TestFiles/ExcelFiles/AscScheme.xlsx
@@ -90,7 +90,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="n">
-        <v>8.14</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="2">
@@ -101,7 +101,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.64</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="3">
@@ -112,7 +112,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>6.02</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="4">
@@ -123,7 +123,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>11.02</v>
+        <v>12.4</v>
       </c>
     </row>
   </sheetData>

--- a/TestFiles/ExcelFiles/AscScheme.xlsx
+++ b/TestFiles/ExcelFiles/AscScheme.xlsx
@@ -90,7 +90,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="n">
-        <v>10.76</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="2">
@@ -101,7 +101,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.15</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="3">
@@ -112,7 +112,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>4.46</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4">
@@ -123,7 +123,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>7.24</v>
+        <v>4.84</v>
       </c>
     </row>
   </sheetData>
